--- a/data/trans_camb/IP04D$notiene-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Provincia-trans_camb.xlsx
@@ -581,7 +581,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,56; 36,39</t>
+          <t>10,07; 36,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,81; 44,22</t>
+          <t>12,23; 44,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 44,88</t>
+          <t>18,16; 44,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 17,66</t>
+          <t>-7,18; 17,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,3; 36,93</t>
+          <t>17,12; 36,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 26,22</t>
+          <t>5,12; 26,42</t>
         </is>
       </c>
     </row>
@@ -705,39 +705,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>46,27; 357,02</t>
+          <t>37,62; 360,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,35; 374,1</t>
+          <t>44,0; 407,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,92; 335,67</t>
+          <t>63,65; 364,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 123,62</t>
+          <t>-29,71; 147,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>79,24; 277,34</t>
+          <t>73,85; 260,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,45; 187,85</t>
+          <t>19,87; 180,46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 22,23</t>
+          <t>5,88; 21,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 2,44</t>
+          <t>-10,42; 2,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,56; 28,45</t>
+          <t>12,08; 28,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 10,64</t>
+          <t>-3,39; 9,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,61; 22,78</t>
+          <t>10,96; 23,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 4,68</t>
+          <t>-4,94; 4,65</t>
         </is>
       </c>
     </row>
@@ -861,39 +861,39 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,57; 448,54</t>
+          <t>41,96; 424,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-80,04; 54,31</t>
+          <t>-81,44; 44,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104,08; 669,19</t>
+          <t>109,09; 699,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 227,3</t>
+          <t>-37,4; 205,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>103,28; 410,27</t>
+          <t>99,77; 413,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 85,92</t>
+          <t>-46,85; 78,12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 7,82</t>
+          <t>-1,06; 7,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 6,24</t>
+          <t>-1,09; 6,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,94</t>
+          <t>-3,04; 1,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 5,99</t>
+          <t>-1,36; 6,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,23</t>
+          <t>-1,09; 3,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,22</t>
+          <t>-0,88; 4,45</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,75; —</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 4,66</t>
+          <t>-3,9; 4,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 5,29</t>
+          <t>-4,45; 5,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 13,79</t>
+          <t>2,96; 13,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 10,77</t>
+          <t>0,68; 10,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,46</t>
+          <t>0,61; 8,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 5,78</t>
+          <t>-0,81; 6,02</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,69; —</t>
+          <t>-15,56; 1894,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,73; —</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 1,37</t>
+          <t>-12,92; 1,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -1,61</t>
+          <t>-15,17; -1,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,48; -1,45</t>
+          <t>-14,14; -1,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -1,43</t>
+          <t>-14,12; -1,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,8; -0,95</t>
+          <t>-9,21; -0,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -1,9</t>
+          <t>-10,11; -1,98</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>17,57; 36,84</t>
+          <t>16,94; 37,09</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,09; 9,79</t>
+          <t>1,11; 9,84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16,55; 36,04</t>
+          <t>16,69; 36,59</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>20,23; 35,07</t>
+          <t>19,98; 34,41</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,07</t>
+          <t>0,53; 5,15</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>12,13; 24,16</t>
+          <t>12,28; 24,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>25,18; 40,42</t>
+          <t>25,32; 40,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,23; 20,04</t>
+          <t>8,65; 19,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30,18; 47,91</t>
+          <t>30,29; 48,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,66; 19,77</t>
+          <t>12,04; 19,66</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,48; 42,81</t>
+          <t>30,31; 42,36</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>307,63; 4655,97</t>
+          <t>292,44; 4555,21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>666,12; 7703,27</t>
+          <t>672,0; 8184,69</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>141,63; 1457,55</t>
+          <t>161,5; 1674,27</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>524,23; 3923,11</t>
+          <t>572,45; 3620,39</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>308,11; 1543,56</t>
+          <t>305,91; 1685,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>775,08; 3391,69</t>
+          <t>782,11; 3917,47</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1721,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,11; -0,18</t>
+          <t>-4,1; -0,03</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,91</t>
+          <t>-1,98; 3,71</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,67</t>
+          <t>-2,08; 1,86</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,84</t>
+          <t>-1,63; 2,67</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,35</t>
+          <t>-2,26; 0,48</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,37</t>
+          <t>-1,32; 2,37</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 436,91</t>
+          <t>-71,62; 396,7</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-90,78; 67,49</t>
+          <t>-90,49; 80,54</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-50,92; 243,1</t>
+          <t>-55,59; 279,29</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1877,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,42</t>
+          <t>6,86; 11,6</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6,52; 13,17</t>
+          <t>6,66; 13,06</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,77</t>
+          <t>8,7; 13,96</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7,05; 13,23</t>
+          <t>6,92; 13,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,79</t>
+          <t>8,29; 11,89</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,07</t>
+          <t>7,46; 12,17</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1953,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>134,44; 351,49</t>
+          <t>131,52; 356,52</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>125,54; 385,4</t>
+          <t>133,5; 387,4</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>168,12; 436,14</t>
+          <t>168,1; 440,27</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>135,48; 402,23</t>
+          <t>135,43; 396,57</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>173,21; 339,98</t>
+          <t>167,17; 347,95</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>158,94; 348,7</t>
+          <t>157,66; 350,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$notiene-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Provincia-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,07; 36,17</t>
+          <t>10,75; 37,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 44,25</t>
+          <t>12,03; 45,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,16; 44,98</t>
+          <t>17,96; 46,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 17,96</t>
+          <t>-9,54; 17,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,12; 36,44</t>
+          <t>18,73; 37,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 26,42</t>
+          <t>5,18; 26,82</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,62; 360,31</t>
+          <t>47,64; 382,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,0; 407,29</t>
+          <t>48,61; 433,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,65; 364,71</t>
+          <t>60,27; 355,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 147,02</t>
+          <t>-37,36; 133,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,85; 260,24</t>
+          <t>75,62; 274,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,87; 180,46</t>
+          <t>19,52; 181,92</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,88; 21,92</t>
+          <t>6,02; 21,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 2,03</t>
+          <t>-10,04; 2,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,08; 28,61</t>
+          <t>12,37; 27,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 9,58</t>
+          <t>-4,21; 10,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 23,03</t>
+          <t>11,22; 22,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 4,65</t>
+          <t>-5,23; 4,41</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,96; 424,11</t>
+          <t>43,6; 441,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,44; 44,2</t>
+          <t>-82,38; 47,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109,09; 699,99</t>
+          <t>106,6; 666,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 205,67</t>
+          <t>-40,99; 210,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,77; 413,55</t>
+          <t>108,5; 407,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 78,12</t>
+          <t>-49,16; 74,71</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 7,32</t>
+          <t>-1,14; 7,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 6,73</t>
+          <t>-1,09; 7,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,94</t>
+          <t>-3,02; 1,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 6,11</t>
+          <t>-1,45; 5,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,96</t>
+          <t>-1,03; 4,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,45</t>
+          <t>-0,92; 4,4</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,75; —</t>
+          <t>-85,74; —</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 4,14</t>
+          <t>-4,34; 4,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 5,06</t>
+          <t>-4,42; 5,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 13,6</t>
+          <t>3,06; 14,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 10,65</t>
+          <t>0,71; 12,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 8,03</t>
+          <t>0,67; 7,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 6,02</t>
+          <t>-0,92; 5,42</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 1894,74</t>
+          <t>-3,0; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,73; —</t>
+          <t>-75,14; 1451,93</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 1,05</t>
+          <t>-12,94; 1,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,17; -1,62</t>
+          <t>-14,25; -1,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-14,14; -1,45</t>
+          <t>-13,19; -1,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,12; -1,46</t>
+          <t>-13,96; -1,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,21; -0,96</t>
+          <t>-9,94; -0,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,11; -1,98</t>
+          <t>-10,34; -1,8</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>16,94; 37,09</t>
+          <t>18,06; 36,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,84</t>
+          <t>1,09; 12,03</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16,69; 36,59</t>
+          <t>17,08; 37,31</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,98; 34,41</t>
+          <t>19,69; 33,58</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,15</t>
+          <t>0,55; 5,15</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>12,28; 24,02</t>
+          <t>12,52; 24,03</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>25,32; 40,19</t>
+          <t>26,58; 41,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,65; 19,52</t>
+          <t>8,69; 19,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30,29; 48,35</t>
+          <t>29,21; 47,83</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,04; 19,66</t>
+          <t>11,32; 20,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,31; 42,36</t>
+          <t>31,23; 42,98</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>292,44; 4555,21</t>
+          <t>292,45; 4349,36</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>672,0; 8184,69</t>
+          <t>670,88; 7942,19</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>161,5; 1674,27</t>
+          <t>169,66; 1452,63</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>572,45; 3620,39</t>
+          <t>495,81; 3426,35</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>305,91; 1685,59</t>
+          <t>295,49; 1708,3</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>782,11; 3917,47</t>
+          <t>787,22; 3542,65</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1721,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,1; -0,03</t>
+          <t>-3,94; -0,1</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,71</t>
+          <t>-1,74; 4,17</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,86</t>
+          <t>-2,35; 1,69</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,67</t>
+          <t>-1,64; 2,95</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,48</t>
+          <t>-2,16; 0,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,37</t>
+          <t>-1,03; 2,6</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-71,62; 396,7</t>
+          <t>-68,08; 541,33</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-90,49; 80,54</t>
+          <t>-87,81; 115,45</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 279,29</t>
+          <t>-53,11; 292,0</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1877,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,6</t>
+          <t>6,72; 11,38</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,06</t>
+          <t>6,42; 13,11</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8,7; 13,96</t>
+          <t>8,52; 13,47</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6,92; 13,2</t>
+          <t>6,98; 12,95</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,29; 11,89</t>
+          <t>8,27; 11,91</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,17</t>
+          <t>7,47; 12,09</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1953,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>131,52; 356,52</t>
+          <t>120,54; 348,25</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>133,5; 387,4</t>
+          <t>126,67; 386,93</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>168,1; 440,27</t>
+          <t>163,7; 410,62</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>135,43; 396,57</t>
+          <t>137,27; 390,23</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>167,17; 347,95</t>
+          <t>172,66; 347,91</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>157,66; 350,6</t>
+          <t>160,47; 351,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$notiene-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Provincia-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de calefacción en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31,72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,62</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>23,68</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>26,91</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31,72</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>15,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,38</t>
+          <t>8,17</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 37,06</t>
+          <t>17,22; 44,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,03; 45,5</t>
+          <t>-10,44; 12,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,96; 46,63</t>
+          <t>11,56; 36,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 17,81</t>
+          <t>3,33; 27,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,73; 37,54</t>
+          <t>18,3; 36,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 26,82</t>
+          <t>-0,4; 16,48</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>157,82%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>145,86%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>165,78%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>157,82%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,64; 382,43</t>
+          <t>61,92; 335,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,61; 433,56</t>
+          <t>-39,1; 91,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60,27; 355,8</t>
+          <t>46,27; 357,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 133,14</t>
+          <t>10,17; 240,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,62; 274,98</t>
+          <t>79,24; 277,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,52; 181,92</t>
+          <t>-1,98; 121,05</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>13,66</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,49</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20,2</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,93</t>
+          <t>-2,8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>0,34</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 21,91</t>
+          <t>12,56; 28,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 2,84</t>
+          <t>-3,43; 11,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,37; 27,98</t>
+          <t>5,71; 22,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 10,11</t>
+          <t>-8,41; 3,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,22; 22,72</t>
+          <t>11,61; 22,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 4,41</t>
+          <t>-4,17; 5,08</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>268,71%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>41,66%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>159,62%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-40,79%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>268,71%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>-32,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-3,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,6; 441,87</t>
+          <t>104,08; 669,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,38; 47,76</t>
+          <t>-38,7; 235,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106,6; 666,2</t>
+          <t>42,57; 448,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,99; 210,02</t>
+          <t>-74,11; 74,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>108,5; 407,71</t>
+          <t>103,28; 410,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 74,71</t>
+          <t>-39,71; 87,48</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,46</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>2,35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>1,29</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 7,2</t>
+          <t>-3,02; 1,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 7,16</t>
+          <t>-1,52; 5,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,93</t>
+          <t>-1,07; 7,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,54</t>
+          <t>-2,14; 5,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,09</t>
+          <t>-1,04; 4,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,4</t>
+          <t>-0,99; 3,97</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-4,54%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>145,17%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>219,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>122,32%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-4,54%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151,7%</t>
+          <t>104,67%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>137,2%</t>
+          <t>124,73%</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,74; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,44</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,65</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,44</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,75</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,65</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 4,18</t>
+          <t>3,35; 13,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 5,52</t>
+          <t>0,66; 12,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 14,68</t>
+          <t>-4,47; 4,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 12,92</t>
+          <t>-4,09; 5,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,52</t>
+          <t>0,77; 7,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 5,42</t>
+          <t>-0,98; 5,8</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-5,49%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-13,71%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>-16,93%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134,54%</t>
+          <t>125,1%</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,0; —</t>
+          <t>-5,69; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,14; 1451,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-4,8</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-4,8</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-4,03</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-5,49</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,8</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-4,8</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 1,26</t>
+          <t>-13,48; -1,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,25; -1,62</t>
+          <t>-12,81; -1,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,19; -1,45</t>
+          <t>-13,62; 1,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,96; -1,46</t>
+          <t>-15,38; -1,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -0,99</t>
+          <t>-9,8; -0,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -1,8</t>
+          <t>-10,31; -1,9</t>
         </is>
       </c>
     </row>
@@ -1291,17 +1293,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-73,4%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1349,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1371,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>26,45</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1,18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>26,04</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3,69</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>26,45</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>3,96</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1396,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,53</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>18,06; 36,89</t>
+          <t>16,55; 36,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,09; 12,03</t>
+          <t>0,0; 6,4</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17,08; 37,31</t>
+          <t>17,57; 36,84</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>1,25; 10,48</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,69; 33,58</t>
+          <t>20,23; 35,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,15</t>
+          <t>0,64; 5,74</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>13,77</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>35,72</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>17,75</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>33,11</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>13,77</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38,86</t>
+          <t>34,54</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1552,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,35</t>
+          <t>35,2</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>12,52; 24,03</t>
+          <t>8,23; 20,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>26,58; 41,1</t>
+          <t>27,42; 43,6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,69; 19,37</t>
+          <t>12,13; 24,16</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29,21; 47,83</t>
+          <t>26,88; 42,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,32; 20,03</t>
+          <t>11,66; 19,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,23; 42,98</t>
+          <t>29,54; 40,92</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>479,54%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1244,11%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>1094,53%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2041,3%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>479,54%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1353,36%</t>
+          <t>2129,55%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1628,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1607,0%</t>
+          <t>1556,05%</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>292,45; 4349,36</t>
+          <t>141,63; 1457,55</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>670,88; 7942,19</t>
+          <t>498,92; 3518,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>169,66; 1452,63</t>
+          <t>307,63; 4655,97</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>495,81; 3426,35</t>
+          <t>688,75; 8033,41</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>295,49; 1708,3</t>
+          <t>308,11; 1543,56</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>787,22; 3542,65</t>
+          <t>740,76; 3256,96</t>
         </is>
       </c>
     </row>
@@ -1683,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,35</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-1,7</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1708,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,1</t>
+          <t>-2,05; 1,67</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 4,17</t>
+          <t>-1,8; 2,92</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,69</t>
+          <t>-4,11; -0,18</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,95</t>
+          <t>-1,82; 3,89</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,52</t>
+          <t>-2,53; 0,35</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,6</t>
+          <t>-1,14; 2,38</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-3,29%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>28,86%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-83,21%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>35,94%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-3,29%</t>
-        </is>
-      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1784,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1804,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-68,08; 541,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1812,17 +1814,17 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-68,15; 423,8</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-87,81; 115,45</t>
+          <t>-90,78; 67,49</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-53,11; 292,0</t>
+          <t>-53,83; 236,73</t>
         </is>
       </c>
     </row>
@@ -1839,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>10,98</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>8,47</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>9,05</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>10,98</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>8,1</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1864,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,63</t>
+          <t>8,3</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,38</t>
+          <t>8,41; 13,77</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6,42; 13,11</t>
+          <t>5,87; 11,25</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,47</t>
+          <t>6,94; 11,42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6,98; 12,95</t>
+          <t>5,62; 10,69</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,91</t>
+          <t>8,22; 11,79</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,09</t>
+          <t>6,54; 10,27</t>
         </is>
       </c>
     </row>
@@ -1915,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>270,36%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>208,73%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>221,73%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>230,24%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>270,36%</t>
-        </is>
-      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>241,97%</t>
+          <t>198,43%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1940,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>236,44%</t>
+          <t>203,82%</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>120,54; 348,25</t>
+          <t>168,12; 436,14</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>126,67; 386,93</t>
+          <t>112,68; 347,46</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>163,7; 410,62</t>
+          <t>134,44; 351,49</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>137,27; 390,23</t>
+          <t>107,85; 332,32</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>172,66; 347,91</t>
+          <t>173,21; 339,98</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>160,47; 351,65</t>
+          <t>141,12; 298,9</t>
         </is>
       </c>
     </row>
